--- a/saidas/classificacao_rascunho.xlsx
+++ b/saidas/classificacao_rascunho.xlsx
@@ -156,7 +156,7 @@
     <t>Colunas `pbe_*`. O PBE Veicular (Inmetro, 2009-2026) lista por versao o tipo de propulsao (coluna propria desde 2021) e o combustivel. Casamento por marca e prefixo do modelo, versao ignorada; cada ano do PBE vai para a vigencia com mais meses naquele ano. `pbe_situacao`: concorda (mesmo conjunto), diverge (`pbe_diferenca` diz o que sobra de cada lado), ausente (o modelo nao aparece no PBE nos anos da vigencia -- ausencia NAO e' evidencia de combustao). A gasolina da transicao flex, anterior ao PBE, nao conta como divergencia. A proposta fica intacta ao lado.</t>
   </si>
   <si>
-    <t>Combustao, Hibrido, Plug-In e Eletrico, mais o combustivel (G, F, D, E). NAO distingue hibrido leve: o Kia Stonic MHEV e o Subaru Forester MHEV estao em Hibrido, o Subaru XV MHEV em Combustao (2021). NAO distingue REEV: o Leapmotor C10 REEV esta' em Plug-In. Onde o nome da versao diz MHEV ou REEV, o nome manda (aba `pbe_mapeamento`). Ate' 2020 nao ha' coluna de propulsao: hibrido sem marcador no nome sai como combustao.</t>
+    <t>Combustao, Hibrido, Plug-In e Eletrico, mais o combustivel (G, F, D, E). NAO distingue hibrido leve: o Kia Stonic MHEV e o Subaru Forester MHEV estao em Hibrido, o Subaru XV MHEV em Combustao (2021); os Stellantis 'HYB' (Pulse, Fastback, Renegade), o Toro de 2026 e o Discovery Sport D200 estao em Hibrido sem MHEV no nome -- 'so' no PBE: hev' contra uma proposta mhev e' provavelmente rotulo do PBE. NAO distingue REEV: o Leapmotor C10 REEV esta' em Plug-In. Onde o nome da versao diz MHEV ou REEV, o nome manda (aba `pbe_mapeamento`). Ate' 2020 nao ha' coluna de propulsao: hibrido sem marcador no nome sai como combustao.</t>
   </si>
   <si>
     <t>Colunas `origem_*`. Cada fonte foi aberta na rodada de validacao; o texto da pagina esta' guardado em dados/bruto/origem_paginas/ e o trecho copiado aparece nele literalmente (testado). `origem_confronto` (confirma, complementa, ajusta_data, contradiz, inconclusivo) e' a LEITURA DO ASSISTENTE da fonte contra a proposta -- confira o trecho antes de aceitar. Aba `origem_fontes` com todas as linhas.</t>
